--- a/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0003T0006Z000C1N94_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0003T0006Z000C1N94_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>7.815604664314936</v>
+        <v>1.270035757951177</v>
       </c>
       <c r="D2" t="n">
-        <v>11.97643254398307</v>
+        <v>1.94617028839725</v>
       </c>
       <c r="E2" t="n">
-        <v>14.03423572629189</v>
+        <v>2.280563305522433</v>
       </c>
       <c r="F2" t="n">
-        <v>12.6855240174852</v>
+        <v>2.061397652841345</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>40.04818581192806</v>
+        <v>6.507830194438311</v>
       </c>
       <c r="D3" t="n">
-        <v>40.74043524244698</v>
+        <v>6.620320726897634</v>
       </c>
       <c r="E3" t="n">
-        <v>14.03423572629189</v>
+        <v>2.280563305522433</v>
       </c>
       <c r="F3" t="n">
-        <v>12.6855240174852</v>
+        <v>2.061397652841345</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>23.78914699362273</v>
+        <v>3.865736386463694</v>
       </c>
       <c r="D4" t="n">
-        <v>26.10166521823914</v>
+        <v>4.24152059796386</v>
       </c>
       <c r="E4" t="n">
-        <v>14.03423572629189</v>
+        <v>2.280563305522433</v>
       </c>
       <c r="F4" t="n">
-        <v>12.6855240174852</v>
+        <v>2.061397652841345</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>5.355695146994893</v>
+        <v>0.8703004613866701</v>
       </c>
       <c r="D5" t="n">
-        <v>45.27543741419411</v>
+        <v>7.357258579806543</v>
       </c>
       <c r="E5" t="n">
-        <v>14.03423572629189</v>
+        <v>2.280563305522433</v>
       </c>
       <c r="F5" t="n">
-        <v>12.6855240174852</v>
+        <v>2.061397652841345</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>27.96730184460583</v>
+        <v>4.544686549748447</v>
       </c>
       <c r="D6" t="n">
-        <v>47.44802597702359</v>
+        <v>7.710304221266334</v>
       </c>
       <c r="E6" t="n">
-        <v>14.03423572629189</v>
+        <v>2.280563305522433</v>
       </c>
       <c r="F6" t="n">
-        <v>12.6855240174852</v>
+        <v>2.061397652841345</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>41.31355819465261</v>
+        <v>6.71345320663105</v>
       </c>
       <c r="D7" t="n">
-        <v>43.15177602342504</v>
+        <v>7.012163603806569</v>
       </c>
       <c r="E7" t="n">
-        <v>14.03423572629189</v>
+        <v>2.280563305522433</v>
       </c>
       <c r="F7" t="n">
-        <v>12.6855240174852</v>
+        <v>2.061397652841345</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
